--- a/InputData/bldgs/EoBSDwEC/Elast of Bldg Svc Demand wrt E Cost.xlsx
+++ b/InputData/bldgs/EoBSDwEC/Elast of Bldg Svc Demand wrt E Cost.xlsx
@@ -1,28 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Dropbox (Energy Innovation)\Desktop\Vensim files from GitHub\EPS US\InputData\bldgs\EoBSDwEC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Dropbox\NEXT Group\20. 프로젝트 관리\2025 에너지 수요전망 모형 구축\EPS 모형\eps-southkorea-3.3.1\InputData\bldgs\EoBSDwEC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344434C8-6702-4CA8-9A05-280406723E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FDBDE7-CFD7-4836-BB02-932032EED100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30960" yWindow="2205" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15750" yWindow="345" windowWidth="21420" windowHeight="19980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="AEO Assumptions" sheetId="3" r:id="rId2"/>
-    <sheet name="EoBSDwEC" sheetId="2" r:id="rId3"/>
+    <sheet name="EoBSDwEC" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>EoBSDwEC Elasticity of Building Service Demand wrt Energy Cost</t>
   </si>
@@ -81,6 +80,15 @@
     <t>Rural Residential</t>
   </si>
   <si>
+    <t>Assumptions to the Annual Energy Outlook 2015</t>
+  </si>
+  <si>
+    <t>Residential Demand Module, Page 29</t>
+  </si>
+  <si>
+    <t>Commercial Demand Module, Page 42</t>
+  </si>
+  <si>
     <t>biomass</t>
   </si>
   <si>
@@ -99,36 +107,31 @@
     <t>Elasticity by Fuel (dimensionless)</t>
   </si>
   <si>
-    <t>Residential Demand Module</t>
-  </si>
-  <si>
-    <t>Commercial Demand Module</t>
+    <t>http://www.eia.gov/forecasts/aeo/assumptions/pdf/residential.pdf</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.eia.gov/outlooks/aeo/assumptions/pdf/RDM_Assumptions.pdf</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.eia.gov/forecasts/aeo/assumptions/pdf/commercial.pdf</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://www.eia.gov/outlooks/aeo/assumptions/pdf/CDM_Assumptions.pdf</t>
-  </si>
-  <si>
-    <t>https://www.eia.gov/outlooks/aeo/assumptions/pdf/rDM_Assumptions.pdf</t>
-  </si>
-  <si>
-    <t>Assumptions to the Annual Energy Outlook 2023</t>
-  </si>
-  <si>
-    <t>Residential Demand Module, Page 10</t>
-  </si>
-  <si>
-    <t>Commercial Demand Module, Page 12</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -136,7 +139,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -144,7 +147,29 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -170,7 +195,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -183,11 +208,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -202,115 +228,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>600925</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>67057</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD44B5EF-D9AC-FE06-7866-DB89594A951B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="4191000"/>
-          <a:ext cx="6087325" cy="2734057"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>600925</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>47951</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0A2935C-7788-A00C-0A39-E609CA2C7CC6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="571500"/>
-          <a:ext cx="6087325" cy="2333951"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -348,9 +269,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -383,26 +304,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -435,26 +339,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -629,17 +516,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -647,141 +534,120 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B10" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B14" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B8" r:id="rId1" xr:uid="{60D76196-89E8-409A-9486-42B6F30B69BB}"/>
+    <hyperlink ref="B10" r:id="rId2" xr:uid="{066E6770-BAAB-40BF-A563-445AD17F0557}"/>
+    <hyperlink ref="B12" r:id="rId3" xr:uid="{AF2FC448-FDD6-41B1-B8CB-98EF03D08B4D}"/>
+    <hyperlink ref="B14" r:id="rId4" xr:uid="{2E043A70-248A-4DA0-A065-F539D1D25837}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B545A04D-0C81-4573-BDE4-77F74558811D}">
-  <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I1" s="6">
-        <v>44986</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>27</v>
-      </c>
-      <c r="I20" s="6">
-        <v>44986</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="3" width="19.85546875" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="2" max="3" width="19.875" customWidth="1"/>
+    <col min="4" max="4" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>17</v>
@@ -793,147 +659,319 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="7">
         <v>-0.3</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="7">
         <v>-0.3</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="7">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3">
-        <v>-0.15</v>
-      </c>
-      <c r="C3">
-        <v>-0.15</v>
-      </c>
-      <c r="D3">
+      <c r="B3" s="7">
+        <v>-0.15</v>
+      </c>
+      <c r="C3" s="7">
+        <v>-0.15</v>
+      </c>
+      <c r="D3" s="7">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4">
-        <v>-0.15</v>
-      </c>
-      <c r="C4">
-        <v>-0.15</v>
-      </c>
-      <c r="D4">
+      <c r="B4" s="7">
+        <v>-0.15</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-0.15</v>
+      </c>
+      <c r="D4" s="7">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5">
-        <v>-0.15</v>
-      </c>
-      <c r="C5">
-        <v>-0.15</v>
-      </c>
-      <c r="D5">
+      <c r="B5" s="7">
+        <v>-0.15</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-0.15</v>
+      </c>
+      <c r="D5" s="7">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6">
-        <v>-0.15</v>
-      </c>
-      <c r="C6">
-        <v>-0.15</v>
-      </c>
-      <c r="D6">
+      <c r="B6" s="7">
+        <v>-0.15</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-0.15</v>
+      </c>
+      <c r="D6" s="7">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7">
-        <v>-0.15</v>
-      </c>
-      <c r="C7">
-        <v>-0.15</v>
-      </c>
-      <c r="D7">
+        <v>22</v>
+      </c>
+      <c r="B7" s="7">
+        <v>-0.15</v>
+      </c>
+      <c r="C7" s="7">
+        <v>-0.15</v>
+      </c>
+      <c r="D7" s="7">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8">
-        <v>-0.15</v>
-      </c>
-      <c r="C8">
-        <v>-0.15</v>
-      </c>
-      <c r="D8">
+        <v>23</v>
+      </c>
+      <c r="B8" s="7">
+        <v>-0.15</v>
+      </c>
+      <c r="C8" s="7">
+        <v>-0.15</v>
+      </c>
+      <c r="D8" s="7">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9">
-        <v>-0.15</v>
-      </c>
-      <c r="C9">
-        <v>-0.15</v>
-      </c>
-      <c r="D9">
+        <v>24</v>
+      </c>
+      <c r="B9" s="7">
+        <v>-0.15</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-0.15</v>
+      </c>
+      <c r="D9" s="7">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10">
-        <v>-0.15</v>
-      </c>
-      <c r="C10">
-        <v>-0.15</v>
-      </c>
-      <c r="D10">
+        <v>25</v>
+      </c>
+      <c r="B10" s="7">
+        <v>-0.15</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-0.15</v>
+      </c>
+      <c r="D10" s="7">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11">
-        <v>-0.15</v>
-      </c>
-      <c r="C11">
-        <v>-0.15</v>
-      </c>
-      <c r="D11">
+        <v>26</v>
+      </c>
+      <c r="B11" s="7">
+        <v>-0.15</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-0.15</v>
+      </c>
+      <c r="D11" s="7">
         <v>-0.25</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2B355BB-6CDF-4E43-AF4D-9B80ED1C1B5A}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9090B1C6-5FEA-4175-AD33-BFB2D228E0F8}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B56DC2A-7F86-4C96-B681-CC13E3FFCF2A}"/>
 </file>